--- a/report_forms/023_road_construction_progress_report_form--report_forms.xlsx
+++ b/report_forms/023_road_construction_progress_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'on_track'}</t>
+          <t>on_track</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'On Track'}</t>
+          <t>On Track</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'delayed'}</t>
+          <t>delayed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Delayed'}</t>
+          <t>Delayed</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'concrete_foundation'}</t>
+          <t>concrete_foundation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Concrete Foundation'}</t>
+          <t>Concrete Foundation</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'structural_frame'}</t>
+          <t>structural_frame</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Structural Frame'}</t>
+          <t>Structural Frame</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'glazing'}</t>
+          <t>glazing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Glazing'}</t>
+          <t>Glazing</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'finishing_work'}</t>
+          <t>finishing_work</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Finishing Work'}</t>
+          <t>Finishing Work</t>
         </is>
       </c>
     </row>
